--- a/Data Packages/Dragonfly_SV1_SN3245_table.xlsx
+++ b/Data Packages/Dragonfly_SV1_SN3245_table.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>measurement</t>
   </si>
@@ -77,19 +77,28 @@
     <t>42</t>
   </si>
   <si>
+    <t>Col_1</t>
+  </si>
+  <si>
+    <t>Col_2</t>
+  </si>
+  <si>
+    <t>Col_3</t>
+  </si>
+  <si>
     <t>resistance</t>
   </si>
   <si>
+    <t>dc</t>
+  </si>
+  <si>
+    <t>Insulation resistance</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>dc</t>
-  </si>
-  <si>
-    <t>Insulation resistance</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>100</t>
@@ -535,7 +544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -547,32 +556,43 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
+      <c r="C4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
